--- a/Interface_IAI.xlsx
+++ b/Interface_IAI.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Buloup\Documents\GIT\Interface_IAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{46308AA1-3458-43F8-8820-85135FF470D2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FB6480-DBA5-47E9-A31A-1F4DBEF2D290}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6720"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Interface_IAI" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="112">
   <si>
     <t>Composants pour cicuit imprimé</t>
   </si>
@@ -145,9 +145,6 @@
     <t>100XBK-ND</t>
   </si>
   <si>
-    <t>R3,R4,R11,R12,R13,R14,R15,R16,R17,R18,R23</t>
-  </si>
-  <si>
     <t>10k</t>
   </si>
   <si>
@@ -160,9 +157,6 @@
     <t>MFR-25FBF52-120R-ND</t>
   </si>
   <si>
-    <t>R19,R20,R21,R22,R24</t>
-  </si>
-  <si>
     <t>2.2k</t>
   </si>
   <si>
@@ -341,12 +335,33 @@
   </si>
   <si>
     <t>Grand total TTC</t>
+  </si>
+  <si>
+    <t>732-12994-ND</t>
+  </si>
+  <si>
+    <t>Entretoise hexagonale M3, polyamide</t>
+  </si>
+  <si>
+    <t>MF-R050-ND</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>MF-R050</t>
+  </si>
+  <si>
+    <t>R3,R4,R11,R12,R13,R14,R15,R16,R17,R18,R23,R25,R26,R28,R30</t>
+  </si>
+  <si>
+    <t>R19,R20,R21,R22,R24,R27,R29</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
   </numFmts>
@@ -902,28 +917,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="8" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="8" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -935,6 +935,23 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1289,1159 +1306,1275 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="52.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="A3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="11" t="s">
+      <c r="F3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>3</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
+        <f>B4*2</f>
         <v>6</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="1">
         <v>0.23</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="1">
         <v>1.38</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" ref="C5:C29" si="0">B5*2</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="1">
         <v>5.1100000000000003</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>10.220000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="1">
         <v>0.15</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="1">
         <v>0.3</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="1">
         <v>0.27</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
+        <f>G7*C7</f>
         <v>0.54</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" ref="H8:H29" si="1">G8*C8</f>
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="E9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G9" s="1">
         <v>0.81</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H9" s="1">
+        <f t="shared" si="1"/>
         <v>1.62</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="2">
-        <v>2</v>
-      </c>
-      <c r="C9" s="2">
+      <c r="B10" s="1">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="1"/>
+        <v>9.9599999999999991</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="1"/>
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="1"/>
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="1"/>
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="1"/>
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0.81</v>
+      </c>
+      <c r="H15" s="1">
+        <f t="shared" si="1"/>
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="1">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="H16" s="1">
+        <f t="shared" si="1"/>
+        <v>9.9599999999999991</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="H17" s="1">
+        <f t="shared" si="1"/>
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="1">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="D18" s="1">
+        <v>100</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="H18" s="1">
+        <f t="shared" si="1"/>
+        <v>0.89999999999999991</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="1">
+        <v>15</v>
+      </c>
+      <c r="C19" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="H19" s="1">
+        <f t="shared" si="1"/>
+        <v>2.6999999999999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="1">
+        <v>3</v>
+      </c>
+      <c r="C20" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D20" s="1">
+        <v>120</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="H20" s="1">
+        <f t="shared" si="1"/>
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" s="1">
+        <v>7</v>
+      </c>
+      <c r="C21" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="H21" s="1">
+        <f t="shared" si="1"/>
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1.81</v>
+      </c>
+      <c r="H22" s="1">
+        <f t="shared" si="1"/>
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1.94</v>
+      </c>
+      <c r="H23" s="1">
+        <f t="shared" si="1"/>
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2.52</v>
+      </c>
+      <c r="H24" s="1">
+        <f t="shared" si="1"/>
+        <v>5.04</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G25" s="1">
+        <v>3.41</v>
+      </c>
+      <c r="H25" s="1">
+        <f t="shared" si="1"/>
+        <v>6.82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="1">
+        <v>2</v>
+      </c>
+      <c r="C26" s="1">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1.66</v>
-      </c>
-      <c r="H9" s="2">
-        <v>6.64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="2">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1.46</v>
-      </c>
-      <c r="H10" s="2">
-        <v>2.92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="2">
-        <v>1</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1.66</v>
-      </c>
-      <c r="H11" s="2">
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="2">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="2">
-        <v>1.46</v>
-      </c>
-      <c r="H12" s="2">
-        <v>2.92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="2">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2">
-        <v>2</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1.66</v>
-      </c>
-      <c r="H13" s="2">
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="2">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2">
-        <v>2</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0.81</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="2">
-        <v>2</v>
-      </c>
-      <c r="C15" s="2">
+      <c r="D26" s="1"/>
+      <c r="E26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="H26" s="1">
+        <f t="shared" si="1"/>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="H27" s="1">
+        <f t="shared" si="1"/>
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2</v>
+      </c>
+      <c r="C28" s="1">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="2">
-        <v>1.66</v>
-      </c>
-      <c r="H15" s="2">
-        <v>6.64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="2">
-        <v>1</v>
-      </c>
-      <c r="C16" s="2">
-        <v>2</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1.66</v>
-      </c>
-      <c r="H16" s="2">
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="2">
+      <c r="D28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="H28" s="1">
+        <f t="shared" si="1"/>
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" s="13">
+        <v>6</v>
+      </c>
+      <c r="C29" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G29" s="13">
+        <v>0.76</v>
+      </c>
+      <c r="H29" s="1">
+        <f t="shared" si="1"/>
+        <v>9.120000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G31" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="5">
+        <f>SUM(H4:H29)</f>
+        <v>92.560000000000031</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="2">
-        <v>10</v>
-      </c>
-      <c r="D17" s="2">
-        <v>100</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0.09</v>
-      </c>
-      <c r="H17" s="2">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="2">
-        <v>11</v>
-      </c>
-      <c r="C18" s="2">
-        <v>22</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0.09</v>
-      </c>
-      <c r="H18" s="2">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="2">
-        <v>3</v>
-      </c>
-      <c r="C19" s="2">
+      <c r="F34" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="2">
-        <v>120</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0.09</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="2">
-        <v>5</v>
-      </c>
-      <c r="C20" s="2">
-        <v>10</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0.09</v>
-      </c>
-      <c r="H20" s="2">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="2">
-        <v>1</v>
-      </c>
-      <c r="C21" s="2">
-        <v>2</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" s="2">
-        <v>1.81</v>
-      </c>
-      <c r="H21" s="2">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="2">
-        <v>1</v>
-      </c>
-      <c r="C22" s="2">
-        <v>2</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22" s="2">
-        <v>1.94</v>
-      </c>
-      <c r="H22" s="2">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="2">
-        <v>1</v>
-      </c>
-      <c r="C23" s="2">
-        <v>2</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23" s="2">
-        <v>2.52</v>
-      </c>
-      <c r="H23" s="2">
-        <v>5.04</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B24" s="2">
-        <v>1</v>
-      </c>
-      <c r="C24" s="2">
-        <v>2</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24" s="2">
-        <v>3.41</v>
-      </c>
-      <c r="H24" s="2">
-        <v>6.82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="2">
-        <v>2</v>
-      </c>
-      <c r="C25" s="2">
-        <v>4</v>
-      </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25" s="2">
-        <v>0.95</v>
-      </c>
-      <c r="H25" s="2">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="2">
-        <v>1</v>
-      </c>
-      <c r="C26" s="2">
-        <v>2</v>
-      </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0.95</v>
-      </c>
-      <c r="H26" s="2">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B27" s="2">
-        <v>2</v>
-      </c>
-      <c r="C27" s="2">
-        <v>4</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="H34" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1">
+        <v>2</v>
+      </c>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G35" s="1">
+        <v>90.34</v>
+      </c>
+      <c r="H35" s="1">
+        <v>180.68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G37" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0.19</v>
-      </c>
-      <c r="H27" s="2">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G29" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H29" s="10">
-        <v>74.900000000000006</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B33" s="2">
-        <v>1</v>
-      </c>
-      <c r="C33" s="2">
-        <v>2</v>
-      </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2" t="s">
+      <c r="H37" s="5">
+        <v>180.68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G33" s="2">
-        <v>90.34</v>
-      </c>
-      <c r="H33" s="2">
-        <v>180.68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G35" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H35" s="10">
-        <v>180.68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B39" s="2">
-        <v>1</v>
-      </c>
-      <c r="C39" s="2">
-        <v>2</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G39" s="2">
-        <v>29.42</v>
-      </c>
-      <c r="H39" s="2">
-        <v>58.84</v>
-      </c>
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1</v>
+      </c>
+      <c r="C41" s="1">
+        <v>2</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G41" s="1">
+        <v>29.42</v>
+      </c>
+      <c r="H41" s="1">
+        <v>58.84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B42" s="1">
+        <v>1</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="2">
-        <v>1</v>
-      </c>
-      <c r="C40" s="2">
-        <v>2</v>
-      </c>
-      <c r="D40" s="2" t="s">
+      <c r="G42" s="1">
+        <v>1.34</v>
+      </c>
+      <c r="H42" s="1">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="2" t="s">
+      <c r="B43" s="1">
+        <v>2</v>
+      </c>
+      <c r="C43" s="1">
+        <v>4</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G40" s="2">
+      <c r="E43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G43" s="1">
+        <v>1.26</v>
+      </c>
+      <c r="H43" s="1">
+        <v>5.04</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1</v>
+      </c>
+      <c r="C44" s="1">
+        <v>2</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1.02</v>
+      </c>
+      <c r="H44" s="1">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="1">
+        <v>8</v>
+      </c>
+      <c r="C45" s="1">
+        <v>16</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G45" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H45" s="1">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46" s="1">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G46" s="1">
+        <v>4.08</v>
+      </c>
+      <c r="H46" s="1">
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B47" s="1">
+        <v>2</v>
+      </c>
+      <c r="C47" s="1">
+        <v>4</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G47" s="1">
         <v>1.34</v>
       </c>
-      <c r="H40" s="2">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="H47" s="1">
+        <v>5.36</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" s="1">
+        <v>1</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B49" s="1">
+        <v>1</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B41" s="2">
-        <v>2</v>
-      </c>
-      <c r="C41" s="2">
-        <v>4</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G41" s="2">
+      <c r="G49" s="1">
         <v>1.26</v>
       </c>
-      <c r="H41" s="2">
-        <v>5.04</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="2">
-        <v>1</v>
-      </c>
-      <c r="C42" s="2">
-        <v>2</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G42" s="2">
-        <v>1.02</v>
-      </c>
-      <c r="H42" s="2">
-        <v>2.04</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B43" s="2">
-        <v>8</v>
-      </c>
-      <c r="C43" s="2">
-        <v>16</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G43" s="2">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="H43" s="2">
-        <v>17.600000000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B44" s="2">
-        <v>1</v>
-      </c>
-      <c r="C44" s="2">
-        <v>2</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G44" s="2">
-        <v>4.08</v>
-      </c>
-      <c r="H44" s="2">
-        <v>8.16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B45" s="2">
-        <v>2</v>
-      </c>
-      <c r="C45" s="2">
-        <v>4</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G45" s="2">
-        <v>1.34</v>
-      </c>
-      <c r="H45" s="2">
-        <v>5.36</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B46" s="2">
-        <v>1</v>
-      </c>
-      <c r="C46" s="2">
-        <v>2</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="2" t="s">
+      <c r="H49" s="1">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G46" s="2">
-        <v>0.98</v>
-      </c>
-      <c r="H46" s="2">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="B50" s="1">
+        <v>1</v>
+      </c>
+      <c r="C50" s="1">
+        <v>2</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B47" s="2">
-        <v>1</v>
-      </c>
-      <c r="C47" s="2">
-        <v>2</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G47" s="2">
-        <v>1.26</v>
-      </c>
-      <c r="H47" s="2">
-        <v>2.52</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+      <c r="E50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B48" s="2">
-        <v>1</v>
-      </c>
-      <c r="C48" s="2">
-        <v>2</v>
-      </c>
-      <c r="D48" s="2" t="s">
+      <c r="G50" s="1">
+        <v>4.66</v>
+      </c>
+      <c r="H50" s="1">
+        <v>9.32</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="2" t="s">
+      <c r="B51" s="1">
+        <v>3</v>
+      </c>
+      <c r="C51" s="1">
+        <v>6</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G48" s="2">
-        <v>4.66</v>
-      </c>
-      <c r="H48" s="2">
-        <v>9.32</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+      <c r="E51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B49" s="2">
-        <v>3</v>
-      </c>
-      <c r="C49" s="2">
-        <v>6</v>
-      </c>
-      <c r="D49" s="2" t="s">
+      <c r="G51" s="1">
+        <v>6.74</v>
+      </c>
+      <c r="H51" s="1">
+        <v>40.44</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="2" t="s">
+      <c r="B52" s="1">
+        <v>1</v>
+      </c>
+      <c r="C52" s="1">
+        <v>2</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G49" s="2">
-        <v>6.74</v>
-      </c>
-      <c r="H49" s="2">
-        <v>40.44</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
+      <c r="E52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B50" s="2">
-        <v>1</v>
-      </c>
-      <c r="C50" s="2">
-        <v>2</v>
-      </c>
-      <c r="D50" s="2" t="s">
+      <c r="G52" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="H52" s="1">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G54" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H54" s="5">
+        <v>166.36</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F56" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="2" t="s">
+      <c r="G56" s="9"/>
+      <c r="H56" s="3">
+        <f>H31+H37+H54</f>
+        <v>439.6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F57" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="G50" s="2">
-        <v>6.2</v>
-      </c>
-      <c r="H50" s="2">
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G52" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H52" s="10">
-        <v>166.36</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F54" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="G54" s="5"/>
-      <c r="H54" s="6">
-        <v>421.94</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F55" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="G55" s="8"/>
-      <c r="H55" s="9">
-        <v>506.33</v>
+      <c r="G57" s="11"/>
+      <c r="H57" s="4">
+        <f>H56*1.2</f>
+        <v>527.52</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A30:H31"/>
-    <mergeCell ref="A36:H37"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="A32:H33"/>
+    <mergeCell ref="A38:H39"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F57:G57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Interface_IAI.xlsx
+++ b/Interface_IAI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Buloup\Documents\GIT\Interface_IAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FB6480-DBA5-47E9-A31A-1F4DBEF2D290}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C80EF1-40B5-4F4A-87C3-1C3DAFFFC69D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="119">
   <si>
     <t>Composants pour cicuit imprimé</t>
   </si>
@@ -28,15 +28,6 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>Qty</t>
-  </si>
-  <si>
-    <t>Qty totale</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
     <t>Fournisseur</t>
   </si>
   <si>
@@ -232,105 +223,6 @@
     <t>B5452603</t>
   </si>
   <si>
-    <t>Boitier</t>
-  </si>
-  <si>
-    <t>Boîtier aluminium 160 × 103 × 53 mm</t>
-  </si>
-  <si>
-    <t>Hammond 1455N1601</t>
-  </si>
-  <si>
-    <t>HM979-ND</t>
-  </si>
-  <si>
-    <t>DA-15 mâle à souder (X3)</t>
-  </si>
-  <si>
-    <t>Amphenol L717SDA15P</t>
-  </si>
-  <si>
-    <t>L717SDA15P-ND</t>
-  </si>
-  <si>
-    <t>DA-15 femelle à souder (X1, X4)</t>
-  </si>
-  <si>
-    <t>Amphenol L77SDA15S</t>
-  </si>
-  <si>
-    <t>L77SDA15S-ND</t>
-  </si>
-  <si>
-    <t>DE-9 femelle à souder (X2)</t>
-  </si>
-  <si>
-    <t>Amphenol L77SDE09S</t>
-  </si>
-  <si>
-    <t>L77SDE09S-ND</t>
-  </si>
-  <si>
-    <t>Vis de verrouillage 4-40 pour D-Sub (2 par connecteur)</t>
-  </si>
-  <si>
-    <t>Molex 1731120014</t>
-  </si>
-  <si>
-    <t>1731120014-ND</t>
-  </si>
-  <si>
-    <t>Jack d'alimentation à monter en face (X5)</t>
-  </si>
-  <si>
-    <t>Switchcraft 722A</t>
-  </si>
-  <si>
-    <t>SC1049-ND</t>
-  </si>
-  <si>
-    <t>DA-15 mâle à souder  (pour X1, X4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DE-9 mâle à souder (pour X2) </t>
-  </si>
-  <si>
-    <t>Amphenol L717SDE09P</t>
-  </si>
-  <si>
-    <t>L717SDE09P-ND</t>
-  </si>
-  <si>
-    <t>DA-15 femelle à souder - X3 (SCON PULSE + feedback)</t>
-  </si>
-  <si>
-    <t>jack Switchcraft 722A (pour X5)</t>
-  </si>
-  <si>
-    <t>Switchcraft S760</t>
-  </si>
-  <si>
-    <t>SC1052-ND</t>
-  </si>
-  <si>
-    <t>Enveloppe isolation DA-15</t>
-  </si>
-  <si>
-    <t>Amphenol 17E165715</t>
-  </si>
-  <si>
-    <t>664-17E165715-ND</t>
-  </si>
-  <si>
-    <t>Enveloppe isolation DE-9</t>
-  </si>
-  <si>
-    <t>Amphenol 17E165709</t>
-  </si>
-  <si>
-    <t>664-17E165709-ND</t>
-  </si>
-  <si>
     <t>Grand total HT</t>
   </si>
   <si>
@@ -356,6 +248,347 @@
   </si>
   <si>
     <t>R19,R20,R21,R22,R24,R27,R29</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 775-5322</t>
+  </si>
+  <si>
+    <t>Radiospares</t>
+  </si>
+  <si>
+    <t>Coffret mural</t>
+  </si>
+  <si>
+    <t>200-6731</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Rail </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> à couper</t>
+    </r>
+  </si>
+  <si>
+    <t>879-3713</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Un disjoncteur différentiel </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>30mA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>40A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>, type C</t>
+    </r>
+  </si>
+  <si>
+    <t>145-7868</t>
+  </si>
+  <si>
+    <t>175-3722</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Alimentation sur Rail </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DIN</t>
+    </r>
+  </si>
+  <si>
+    <t>175-3725</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 175-3723</t>
+  </si>
+  <si>
+    <t>Filtre EMI (RS )</t>
+  </si>
+  <si>
+    <t>292-818</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Filtre </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>EMI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>RS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> )</t>
+    </r>
+  </si>
+  <si>
+    <t>708-4272</t>
+  </si>
+  <si>
+    <t>916-4336</t>
+  </si>
+  <si>
+    <t>noyaux de ferrite</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">disjoncteur </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>20A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> axe 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">disjoncteur </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>10A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> axe 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Disjoncteur </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>6A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">669-4660 </t>
+  </si>
+  <si>
+    <t>669-4664</t>
+  </si>
+  <si>
+    <t>214-1065</t>
+  </si>
+  <si>
+    <t>669-4673</t>
+  </si>
+  <si>
+    <t>Qté</t>
+  </si>
+  <si>
+    <t>Qté totale</t>
+  </si>
+  <si>
+    <t>Valeur</t>
+  </si>
+  <si>
+    <t>Goulotte (1 paquet de 4 unités)</t>
+  </si>
+  <si>
+    <t>Presse étoupe Ø 4 à 9 mm (1 sachet de 5 unités)</t>
+  </si>
+  <si>
+    <t>Presse étoupe Ø 6 à 12 mm  (1 sachet de 5 unités)</t>
+  </si>
+  <si>
+    <t>Presse étoupe Ø 10 à 14 mm  (1 sachet de 5 unités)</t>
+  </si>
+  <si>
+    <t>Presse étoupe Ø 8 à 12 mm  (1 sachet de 10 unités)</t>
+  </si>
+  <si>
+    <t>238-3297</t>
+  </si>
+  <si>
+    <t>à déterminer</t>
+  </si>
+  <si>
+    <t>Coffret mural avec protection</t>
+  </si>
+  <si>
+    <t>Fusible</t>
+  </si>
+  <si>
+    <t>Connecteur SubD 37 femelle</t>
+  </si>
+  <si>
+    <t>300-295</t>
+  </si>
+  <si>
+    <t>Connecteur SubD 37 male</t>
+  </si>
+  <si>
+    <t>251-677</t>
+  </si>
+  <si>
+    <t>1 presse étoupe : Câble arrivée alimentation</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2 presses étoupe : câbles vers </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ADWin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>DIO32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> et </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>CO4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>-T)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -365,7 +598,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -534,8 +767,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -713,6 +957,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -917,7 +1167,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -935,6 +1185,8 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -950,8 +1202,12 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1307,64 +1563,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H65"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="52.6640625" customWidth="1"/>
+    <col min="1" max="1" width="31.77734375" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" customWidth="1"/>
     <col min="4" max="4" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
@@ -1374,13 +1632,13 @@
         <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
         <v>0.23</v>
@@ -1389,25 +1647,25 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <f t="shared" ref="C5:C29" si="0">B5*2</f>
+        <f t="shared" ref="C5:C30" si="0">B5*2</f>
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G5" s="1">
         <v>5.1100000000000003</v>
@@ -1416,9 +1674,9 @@
         <v>10.220000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -1428,13 +1686,13 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1">
         <v>0.15</v>
@@ -1443,9 +1701,9 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
@@ -1455,13 +1713,13 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1">
         <v>0.27</v>
@@ -1471,9 +1729,9 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
@@ -1483,25 +1741,25 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="G8" s="1">
         <v>0.41</v>
       </c>
       <c r="H8" s="1">
-        <f t="shared" ref="H8:H29" si="1">G8*C8</f>
+        <f t="shared" ref="H8:H30" si="1">G8*C8</f>
         <v>0.82</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
@@ -1511,13 +1769,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1">
         <v>0.81</v>
@@ -1527,9 +1785,9 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
@@ -1539,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G10" s="1">
         <v>1.66</v>
@@ -1555,9 +1813,9 @@
         <v>9.9599999999999991</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
@@ -1567,13 +1825,13 @@
         <v>2</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="G11" s="1">
         <v>1.46</v>
@@ -1583,9 +1841,9 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
@@ -1595,13 +1853,13 @@
         <v>2</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G12" s="1">
         <v>1.66</v>
@@ -1611,9 +1869,9 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B13" s="1">
         <v>1</v>
@@ -1623,13 +1881,13 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G13" s="1">
         <v>1.46</v>
@@ -1639,9 +1897,9 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
@@ -1651,13 +1909,13 @@
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G14" s="1">
         <v>1.66</v>
@@ -1667,9 +1925,9 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B15" s="1">
         <v>1</v>
@@ -1679,13 +1937,13 @@
         <v>2</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G15" s="1">
         <v>0.81</v>
@@ -1695,9 +1953,9 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B16" s="1">
         <v>3</v>
@@ -1707,13 +1965,13 @@
         <v>6</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G16" s="1">
         <v>1.66</v>
@@ -1723,9 +1981,9 @@
         <v>9.9599999999999991</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B17" s="1">
         <v>1</v>
@@ -1735,13 +1993,13 @@
         <v>2</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G17" s="1">
         <v>1.66</v>
@@ -1751,9 +2009,9 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B18" s="1">
         <v>5</v>
@@ -1766,10 +2024,10 @@
         <v>100</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G18" s="1">
         <v>0.09</v>
@@ -1779,9 +2037,9 @@
         <v>0.89999999999999991</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="B19" s="1">
         <v>15</v>
@@ -1791,13 +2049,13 @@
         <v>30</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G19" s="1">
         <v>0.09</v>
@@ -1807,9 +2065,9 @@
         <v>2.6999999999999997</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B20" s="1">
         <v>3</v>
@@ -1822,10 +2080,10 @@
         <v>120</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G20" s="1">
         <v>0.09</v>
@@ -1835,9 +2093,9 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="B21" s="1">
         <v>7</v>
@@ -1847,13 +2105,13 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G21" s="1">
         <v>0.09</v>
@@ -1863,9 +2121,9 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
@@ -1875,13 +2133,13 @@
         <v>2</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G22" s="1">
         <v>1.81</v>
@@ -1891,9 +2149,9 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B23" s="1">
         <v>1</v>
@@ -1903,13 +2161,13 @@
         <v>2</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G23" s="1">
         <v>1.94</v>
@@ -1919,9 +2177,9 @@
         <v>3.88</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B24" s="1">
         <v>1</v>
@@ -1931,13 +2189,13 @@
         <v>2</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G24" s="1">
         <v>2.52</v>
@@ -1947,9 +2205,9 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B25" s="1">
         <v>1</v>
@@ -1959,13 +2217,13 @@
         <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G25" s="1">
         <v>3.41</v>
@@ -1975,9 +2233,9 @@
         <v>6.82</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B26" s="1">
         <v>2</v>
@@ -1988,10 +2246,10 @@
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G26" s="1">
         <v>0.95</v>
@@ -2001,9 +2259,9 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B27" s="1">
         <v>1</v>
@@ -2014,10 +2272,10 @@
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G27" s="1">
         <v>0.95</v>
@@ -2027,9 +2285,9 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B28" s="1">
         <v>2</v>
@@ -2039,13 +2297,13 @@
         <v>4</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G28" s="1">
         <v>0.19</v>
@@ -2055,11 +2313,11 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B29" s="13">
+        <v>70</v>
+      </c>
+      <c r="B29" s="8">
         <v>6</v>
       </c>
       <c r="C29" s="1">
@@ -2068,12 +2326,12 @@
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G29" s="13">
+        <v>69</v>
+      </c>
+      <c r="G29" s="8">
         <v>0.76</v>
       </c>
       <c r="H29" s="1">
@@ -2081,500 +2339,714 @@
         <v>9.120000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G31" s="5" t="s">
+    <row r="30" spans="1:8">
+      <c r="A30" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="8">
+        <v>1</v>
+      </c>
+      <c r="C30" s="8">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="8">
+        <v>0.41</v>
+      </c>
+      <c r="H30" s="8">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="G32" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H32" s="5">
+        <f>SUM(H4:H30)</f>
+        <v>93.380000000000024</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1">
+        <v>2</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H31" s="5">
-        <f>SUM(H4:H29)</f>
-        <v>92.560000000000031</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6" t="s">
+      <c r="G36" s="1">
+        <v>90.34</v>
+      </c>
+      <c r="H36" s="1">
+        <v>180.68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="G38" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H38" s="5">
+        <v>180.68</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="H41" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B35" s="1">
-        <v>1</v>
-      </c>
-      <c r="C35" s="1">
-        <v>2</v>
-      </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G35" s="1">
-        <v>90.34</v>
-      </c>
-      <c r="H35" s="1">
-        <v>180.68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G37" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H37" s="5">
-        <v>180.68</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B41" s="1">
-        <v>1</v>
-      </c>
-      <c r="C41" s="1">
-        <v>2</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G41" s="1">
-        <v>29.42</v>
-      </c>
-      <c r="H41" s="1">
-        <v>58.84</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>74</v>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="B42" s="1">
         <v>1</v>
       </c>
       <c r="C42" s="1">
-        <v>2</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>75</v>
-      </c>
+        <f>B42*2</f>
+        <v>2</v>
+      </c>
+      <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>76</v>
       </c>
       <c r="G42" s="1">
-        <v>1.34</v>
+        <v>97.34</v>
       </c>
       <c r="H42" s="1">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
+        <f>G42*C42</f>
+        <v>194.68</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" s="1">
+        <v>1</v>
+      </c>
+      <c r="C43" s="1">
+        <f t="shared" ref="C43:C60" si="2">B43*2</f>
+        <v>2</v>
+      </c>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="B43" s="1">
-        <v>2</v>
-      </c>
-      <c r="C43" s="1">
-        <v>4</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>79</v>
       </c>
       <c r="G43" s="1">
-        <v>1.26</v>
+        <v>7.53</v>
       </c>
       <c r="H43" s="1">
-        <v>5.04</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
-        <v>80</v>
+        <f t="shared" ref="H43:H60" si="3">G43*C43</f>
+        <v>15.06</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="15" t="s">
+        <v>104</v>
       </c>
       <c r="B44" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="C44" s="1">
-        <v>2</v>
-      </c>
-      <c r="D44" s="1" t="s">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="1" t="s">
+      <c r="G44" s="1">
+        <v>27.09</v>
+      </c>
+      <c r="H44" s="1">
+        <f t="shared" si="3"/>
+        <v>27.09</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C45" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G45" s="1">
+        <v>7.91</v>
+      </c>
+      <c r="H45" s="1">
+        <f t="shared" si="3"/>
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B46" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C46" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G46" s="1">
+        <v>7.05</v>
+      </c>
+      <c r="H46" s="1">
+        <f t="shared" si="3"/>
+        <v>7.05</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C47" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G47" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="H47" s="1">
+        <f t="shared" si="3"/>
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B48" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C48" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G48" s="1">
+        <v>5.43</v>
+      </c>
+      <c r="H48" s="1">
+        <f t="shared" si="3"/>
+        <v>5.43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="B49" s="17">
+        <v>1</v>
+      </c>
+      <c r="C49" s="17">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="D49" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="B50" s="17">
+        <v>1</v>
+      </c>
+      <c r="C50" s="17">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G44" s="1">
-        <v>1.02</v>
-      </c>
-      <c r="H44" s="1">
-        <v>2.04</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
+      <c r="B51" s="1">
+        <v>1</v>
+      </c>
+      <c r="C51" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G51" s="1">
+        <v>244.52</v>
+      </c>
+      <c r="H51" s="1">
+        <f t="shared" si="3"/>
+        <v>489.04</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B52" s="1">
+        <v>3</v>
+      </c>
+      <c r="C52" s="1">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B45" s="1">
+      <c r="G52" s="1">
+        <v>22.77</v>
+      </c>
+      <c r="H52" s="1">
+        <f t="shared" si="3"/>
+        <v>136.62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="B53" s="1">
+        <v>1</v>
+      </c>
+      <c r="C53" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G53" s="1">
+        <v>20.64</v>
+      </c>
+      <c r="H53" s="1">
+        <f t="shared" si="3"/>
+        <v>41.28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54" s="8">
+        <v>1</v>
+      </c>
+      <c r="C54" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G54" s="1">
+        <v>13.32</v>
+      </c>
+      <c r="H54" s="1">
+        <f t="shared" si="3"/>
+        <v>26.64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55" s="8">
+        <v>1</v>
+      </c>
+      <c r="C55" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G55" s="1">
+        <v>13.32</v>
+      </c>
+      <c r="H55" s="1">
+        <f t="shared" si="3"/>
+        <v>26.64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B56" s="8">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G56" s="1">
+        <v>67.75</v>
+      </c>
+      <c r="H56" s="1">
+        <f t="shared" si="3"/>
+        <v>135.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B57" s="1">
+        <v>1</v>
+      </c>
+      <c r="C57" s="1">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G57" s="1">
+        <v>52.9</v>
+      </c>
+      <c r="H57" s="1">
+        <f t="shared" si="3"/>
+        <v>105.8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B58" s="1">
+        <v>4</v>
+      </c>
+      <c r="C58" s="1">
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="C45" s="1">
-        <v>16</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G45" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="H45" s="1">
-        <v>17.600000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B46" s="1">
-        <v>1</v>
-      </c>
-      <c r="C46" s="1">
-        <v>2</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G46" s="1">
-        <v>4.08</v>
-      </c>
-      <c r="H46" s="1">
-        <v>8.16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B47" s="1">
-        <v>2</v>
-      </c>
-      <c r="C47" s="1">
-        <v>4</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G47" s="1">
-        <v>1.34</v>
-      </c>
-      <c r="H47" s="1">
-        <v>5.36</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B48" s="1">
-        <v>1</v>
-      </c>
-      <c r="C48" s="1">
-        <v>2</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="1" t="s">
+      <c r="D58" s="1"/>
+      <c r="E58" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F58" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="G48" s="1">
-        <v>0.98</v>
-      </c>
-      <c r="H48" s="1">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B49" s="1">
-        <v>1</v>
-      </c>
-      <c r="C49" s="1">
-        <v>2</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G49" s="1">
-        <v>1.26</v>
-      </c>
-      <c r="H49" s="1">
-        <v>2.52</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B50" s="1">
-        <v>1</v>
-      </c>
-      <c r="C50" s="1">
-        <v>2</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G50" s="1">
-        <v>4.66</v>
-      </c>
-      <c r="H50" s="1">
-        <v>9.32</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B51" s="1">
-        <v>3</v>
-      </c>
-      <c r="C51" s="1">
-        <v>6</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G51" s="1">
-        <v>6.74</v>
-      </c>
-      <c r="H51" s="1">
-        <v>40.44</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B52" s="1">
-        <v>1</v>
-      </c>
-      <c r="C52" s="1">
-        <v>2</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G52" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="H52" s="1">
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G54" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H54" s="5">
-        <v>166.36</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F56" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="G56" s="9"/>
-      <c r="H56" s="3">
-        <f>H31+H37+H54</f>
-        <v>439.6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F57" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="G57" s="11"/>
-      <c r="H57" s="4">
-        <f>H56*1.2</f>
-        <v>527.52</v>
+      <c r="G58" s="1">
+        <v>10.46</v>
+      </c>
+      <c r="H58" s="1">
+        <f t="shared" si="3"/>
+        <v>83.68</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B59" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="C59" s="17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E59" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F59" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="G59" s="17">
+        <v>7.89</v>
+      </c>
+      <c r="H59" s="17">
+        <f t="shared" si="3"/>
+        <v>7.89</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B60" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="C60" s="17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D60" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="E60" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F60" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="G60" s="17">
+        <v>2.77</v>
+      </c>
+      <c r="H60" s="17">
+        <f t="shared" si="3"/>
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="19"/>
+      <c r="B61" s="14"/>
+      <c r="C61" s="14"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="G62" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H62" s="5">
+        <f>SUM(H42:H60)</f>
+        <v>1319.78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="F64" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G64" s="11"/>
+      <c r="H64" s="3">
+        <f>H32+H38+H62</f>
+        <v>1593.8400000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="6:8">
+      <c r="F65" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G65" s="13"/>
+      <c r="H65" s="4">
+        <f>H64*1.2</f>
+        <v>1912.6080000000002</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A32:H33"/>
-    <mergeCell ref="A38:H39"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="A33:H34"/>
+    <mergeCell ref="A39:H40"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="F65:G65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Interface_IAI.xlsx
+++ b/Interface_IAI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Buloup\Documents\GIT\Interface_IAI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\buloup\Documents\GIT\Interface_IAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C80EF1-40B5-4F4A-87C3-1C3DAFFFC69D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3665356-7B11-4422-AE5C-DD24D205BFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Interface_IAI" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="110">
   <si>
     <t>Composants pour cicuit imprimé</t>
   </si>
@@ -475,15 +475,6 @@
     <t xml:space="preserve">669-4660 </t>
   </si>
   <si>
-    <t>669-4664</t>
-  </si>
-  <si>
-    <t>214-1065</t>
-  </si>
-  <si>
-    <t>669-4673</t>
-  </si>
-  <si>
     <t>Qté</t>
   </si>
   <si>
@@ -496,33 +487,15 @@
     <t>Goulotte (1 paquet de 4 unités)</t>
   </si>
   <si>
-    <t>Presse étoupe Ø 4 à 9 mm (1 sachet de 5 unités)</t>
-  </si>
-  <si>
-    <t>Presse étoupe Ø 6 à 12 mm  (1 sachet de 5 unités)</t>
-  </si>
-  <si>
-    <t>Presse étoupe Ø 10 à 14 mm  (1 sachet de 5 unités)</t>
-  </si>
-  <si>
-    <t>Presse étoupe Ø 8 à 12 mm  (1 sachet de 10 unités)</t>
-  </si>
-  <si>
     <t>238-3297</t>
   </si>
   <si>
-    <t>à déterminer</t>
-  </si>
-  <si>
     <t>Coffret mural avec protection</t>
   </si>
   <si>
     <t>Fusible</t>
   </si>
   <si>
-    <t>Connecteur SubD 37 femelle</t>
-  </si>
-  <si>
     <t>300-295</t>
   </si>
   <si>
@@ -532,63 +505,10 @@
     <t>251-677</t>
   </si>
   <si>
-    <t>1 presse étoupe : Câble arrivée alimentation</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">2 presses étoupe : câbles vers </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>ADWin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>DIO32</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t xml:space="preserve"> et </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>CO4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>-T)</t>
-    </r>
+    <t>Presse-étoupe Ø 4 à 9 mm (1 sachet de 5 unités)</t>
+  </si>
+  <si>
+    <t>Capot connecteur SubD 37</t>
   </si>
 </sst>
 </file>
@@ -961,7 +881,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1170,7 +1090,7 @@
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="8" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1185,8 +1105,8 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1202,12 +1122,14 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1563,13 +1485,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H65"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:H60"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.77734375" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="18.88671875" customWidth="1"/>
+    <col min="1" max="1" width="45.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="19" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1599,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>99</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>2</v>
@@ -1627,7 +1549,7 @@
       <c r="B4" s="1">
         <v>3</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="18">
         <f>B4*2</f>
         <v>6</v>
       </c>
@@ -1654,7 +1576,7 @@
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="18">
         <f t="shared" ref="C5:C30" si="0">B5*2</f>
         <v>2</v>
       </c>
@@ -1681,7 +1603,7 @@
       <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1708,7 +1630,7 @@
       <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1736,7 +1658,7 @@
       <c r="B8" s="1">
         <v>1</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1764,7 +1686,7 @@
       <c r="B9" s="1">
         <v>1</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1792,7 +1714,7 @@
       <c r="B10" s="1">
         <v>3</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="18">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1820,7 +1742,7 @@
       <c r="B11" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1848,7 +1770,7 @@
       <c r="B12" s="1">
         <v>1</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1876,7 +1798,7 @@
       <c r="B13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1904,7 +1826,7 @@
       <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1932,7 +1854,7 @@
       <c r="B15" s="1">
         <v>1</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1960,7 +1882,7 @@
       <c r="B16" s="1">
         <v>3</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="18">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1988,7 +1910,7 @@
       <c r="B17" s="1">
         <v>1</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -2016,7 +1938,7 @@
       <c r="B18" s="1">
         <v>5</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="18">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2044,7 +1966,7 @@
       <c r="B19" s="1">
         <v>15</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="18">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -2072,7 +1994,7 @@
       <c r="B20" s="1">
         <v>3</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="18">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -2100,7 +2022,7 @@
       <c r="B21" s="1">
         <v>7</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="18">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -2128,7 +2050,7 @@
       <c r="B22" s="1">
         <v>1</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -2156,7 +2078,7 @@
       <c r="B23" s="1">
         <v>1</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -2184,7 +2106,7 @@
       <c r="B24" s="1">
         <v>1</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -2212,7 +2134,7 @@
       <c r="B25" s="1">
         <v>1</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -2240,7 +2162,7 @@
       <c r="B26" s="1">
         <v>2</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="18">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -2266,7 +2188,7 @@
       <c r="B27" s="1">
         <v>1</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -2292,7 +2214,7 @@
       <c r="B28" s="1">
         <v>2</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="18">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -2317,10 +2239,10 @@
       <c r="A29" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="1">
         <v>6</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="18">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -2331,7 +2253,7 @@
       <c r="F29" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="1">
         <v>0.76</v>
       </c>
       <c r="H29" s="1">
@@ -2340,13 +2262,13 @@
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B30" s="8">
-        <v>1</v>
-      </c>
-      <c r="C30" s="8">
+      <c r="A30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1</v>
+      </c>
+      <c r="C30" s="18">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -2357,23 +2279,13 @@
       <c r="F30" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="1">
         <v>0.41</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="1">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
     </row>
     <row r="32" spans="1:8">
       <c r="G32" s="5" t="s">
@@ -2411,13 +2323,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>99</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>2</v>
@@ -2439,7 +2351,7 @@
       <c r="B36" s="1">
         <v>1</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="18">
         <v>2</v>
       </c>
       <c r="D36" s="1"/>
@@ -2466,7 +2378,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -2491,13 +2403,13 @@
         <v>1</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>99</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>2</v>
@@ -2513,15 +2425,15 @@
       </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="7" t="s">
         <v>78</v>
       </c>
       <c r="B42" s="1">
-        <v>1</v>
-      </c>
-      <c r="C42" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C42" s="18">
         <f>B42*2</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
@@ -2535,18 +2447,18 @@
       </c>
       <c r="H42" s="1">
         <f>G42*C42</f>
-        <v>194.68</v>
+        <v>97.34</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="7" t="s">
         <v>80</v>
       </c>
       <c r="B43" s="1">
         <v>1</v>
       </c>
-      <c r="C43" s="1">
-        <f t="shared" ref="C43:C60" si="2">B43*2</f>
+      <c r="C43" s="18">
+        <f t="shared" ref="C43:C55" si="2">B43*2</f>
         <v>2</v>
       </c>
       <c r="D43" s="1"/>
@@ -2560,18 +2472,18 @@
         <v>7.53</v>
       </c>
       <c r="H43" s="1">
-        <f t="shared" ref="H43:H60" si="3">G43*C43</f>
+        <f t="shared" ref="H43:H55" si="3">G43*C43</f>
         <v>15.06</v>
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="15" t="s">
-        <v>104</v>
+      <c r="A44" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="B44" s="1">
         <v>0.5</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C44" s="18">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2591,15 +2503,15 @@
       </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="15" t="s">
-        <v>105</v>
+      <c r="A45" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="B45" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="C45" s="1">
+        <v>1</v>
+      </c>
+      <c r="C45" s="18">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1" t="s">
@@ -2613,17 +2525,17 @@
       </c>
       <c r="H45" s="1">
         <f t="shared" si="3"/>
-        <v>7.91</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="15" t="s">
-        <v>106</v>
+      <c r="A46" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="B46" s="1">
         <v>0.5</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="18">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2632,24 +2544,24 @@
         <v>77</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G46" s="1">
-        <v>7.05</v>
+        <v>244.52</v>
       </c>
       <c r="H46" s="1">
         <f t="shared" si="3"/>
-        <v>7.05</v>
+        <v>244.52</v>
       </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="15" t="s">
-        <v>108</v>
+      <c r="A47" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="B47" s="1">
         <v>0.5</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47" s="18">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2658,24 +2570,24 @@
         <v>77</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="G47" s="1">
-        <v>6.7</v>
+        <v>22.77</v>
       </c>
       <c r="H47" s="1">
         <f t="shared" si="3"/>
-        <v>6.7</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="15" t="s">
-        <v>107</v>
+      <c r="A48" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="B48" s="1">
         <v>0.5</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C48" s="18">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2684,360 +2596,228 @@
         <v>77</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="G48" s="1">
-        <v>5.43</v>
+        <v>20.64</v>
       </c>
       <c r="H48" s="1">
         <f t="shared" si="3"/>
-        <v>5.43</v>
+        <v>20.64</v>
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="B49" s="17">
-        <v>1</v>
-      </c>
-      <c r="C49" s="17">
+      <c r="A49" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C49" s="18">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="D49" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="E49" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="17">
+      <c r="F49" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G49" s="1">
+        <v>13.32</v>
+      </c>
+      <c r="H49" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="B50" s="17">
-        <v>1</v>
-      </c>
-      <c r="C50" s="17">
+      <c r="A50" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B50" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C50" s="18">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="D50" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="E50" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="17">
+      <c r="F50" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G50" s="1">
+        <v>13.32</v>
+      </c>
+      <c r="H50" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>13.32</v>
       </c>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="15" t="s">
-        <v>82</v>
+      <c r="A51" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="B51" s="1">
-        <v>1</v>
-      </c>
-      <c r="C51" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C51" s="18">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1" t="s">
         <v>77</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="G51" s="1">
-        <v>244.52</v>
+        <v>67.75</v>
       </c>
       <c r="H51" s="1">
         <f t="shared" si="3"/>
-        <v>489.04</v>
+        <v>67.75</v>
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="15" t="s">
-        <v>85</v>
+      <c r="A52" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="B52" s="1">
-        <v>3</v>
-      </c>
-      <c r="C52" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C52" s="18">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1" t="s">
         <v>77</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G52" s="1">
-        <v>22.77</v>
+        <v>52.9</v>
       </c>
       <c r="H52" s="1">
         <f t="shared" si="3"/>
-        <v>136.62</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="15" t="s">
-        <v>96</v>
+      <c r="A53" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="B53" s="1">
-        <v>1</v>
-      </c>
-      <c r="C53" s="1">
+        <v>4</v>
+      </c>
+      <c r="C53" s="18">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>84</v>
+      <c r="F53" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="G53" s="1">
-        <v>20.64</v>
+        <v>10.46</v>
       </c>
       <c r="H53" s="1">
         <f t="shared" si="3"/>
-        <v>41.28</v>
+        <v>83.68</v>
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B54" s="8">
-        <v>1</v>
-      </c>
-      <c r="C54" s="1">
+      <c r="A54" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" s="15">
+        <v>1</v>
+      </c>
+      <c r="C54" s="16">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1" t="s">
+      <c r="D54" s="16"/>
+      <c r="E54" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="G54" s="1">
-        <v>13.32</v>
-      </c>
-      <c r="H54" s="1">
+      <c r="F54" t="s">
+        <v>105</v>
+      </c>
+      <c r="G54" s="15">
+        <v>7.89</v>
+      </c>
+      <c r="H54" s="15">
         <f t="shared" si="3"/>
-        <v>26.64</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="B55" s="8">
-        <v>1</v>
-      </c>
-      <c r="C55" s="1">
+      <c r="A55" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B55" s="15">
+        <v>1</v>
+      </c>
+      <c r="C55" s="16">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1" t="s">
+      <c r="D55" s="16"/>
+      <c r="E55" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G55" s="1">
-        <v>13.32</v>
-      </c>
-      <c r="H55" s="1">
+      <c r="F55" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="G55" s="15">
+        <v>4.92</v>
+      </c>
+      <c r="H55" s="15">
         <f t="shared" si="3"/>
-        <v>26.64</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B56" s="8">
-        <v>1</v>
-      </c>
-      <c r="C56" s="1">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G56" s="1">
-        <v>67.75</v>
-      </c>
-      <c r="H56" s="1">
-        <f t="shared" si="3"/>
-        <v>135.5</v>
-      </c>
+      <c r="A56" s="8"/>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B57" s="1">
-        <v>1</v>
-      </c>
-      <c r="C57" s="1">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G57" s="1">
-        <v>52.9</v>
-      </c>
-      <c r="H57" s="1">
-        <f t="shared" si="3"/>
-        <v>105.8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="B58" s="1">
-        <v>4</v>
-      </c>
-      <c r="C58" s="1">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F58" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="G58" s="1">
-        <v>10.46</v>
-      </c>
-      <c r="H58" s="1">
-        <f t="shared" si="3"/>
-        <v>83.68</v>
+      <c r="G57" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H57" s="5">
+        <f>SUM(H42:H55)</f>
+        <v>699.83</v>
       </c>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B59" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="C59" s="17">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="E59" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F59" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="G59" s="17">
-        <v>7.89</v>
-      </c>
-      <c r="H59" s="17">
-        <f t="shared" si="3"/>
-        <v>7.89</v>
+      <c r="F59" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G59" s="11"/>
+      <c r="H59" s="3">
+        <f>H32+H38+H57</f>
+        <v>973.8900000000001</v>
       </c>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B60" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="C60" s="17">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="E60" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="F60" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="G60" s="17">
-        <v>2.77</v>
-      </c>
-      <c r="H60" s="17">
-        <f t="shared" si="3"/>
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="19"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="G62" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H62" s="5">
-        <f>SUM(H42:H60)</f>
-        <v>1319.78</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="F64" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G64" s="11"/>
-      <c r="H64" s="3">
-        <f>H32+H38+H62</f>
-        <v>1593.8400000000001</v>
-      </c>
-    </row>
-    <row r="65" spans="6:8">
-      <c r="F65" s="12" t="s">
+      <c r="F60" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="G65" s="13"/>
-      <c r="H65" s="4">
-        <f>H64*1.2</f>
-        <v>1912.6080000000002</v>
+      <c r="G60" s="13"/>
+      <c r="H60" s="4">
+        <f>H59*1.2</f>
+        <v>1168.6680000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3045,8 +2825,8 @@
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A33:H34"/>
     <mergeCell ref="A39:H40"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="F60:G60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Interface_IAI.xlsx
+++ b/Interface_IAI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\buloup\Documents\GIT\Interface_IAI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Buloup\Documents\GIT\Interface_IAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3665356-7B11-4422-AE5C-DD24D205BFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A738DB8-9050-474F-BB1D-D3B5A4C78D7F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="114">
   <si>
     <t>Composants pour cicuit imprimé</t>
   </si>
@@ -509,6 +509,18 @@
   </si>
   <si>
     <t>Capot connecteur SubD 37</t>
+  </si>
+  <si>
+    <t>498-2710</t>
+  </si>
+  <si>
+    <t>Connecteur CEI Droit C20 Schurter, Panneau Mâle</t>
+  </si>
+  <si>
+    <t>295-8759</t>
+  </si>
+  <si>
+    <t>Connecteur CEI Droit C19 Schurter, Câble</t>
   </si>
 </sst>
 </file>
@@ -1107,6 +1119,14 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1122,14 +1142,6 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1485,36 +1497,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H60"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:H62"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="45.140625" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" style="19" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="1" max="1" width="45.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="14" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="6" t="s">
@@ -1523,7 +1535,7 @@
       <c r="B3" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="12" t="s">
         <v>99</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -1549,7 +1561,7 @@
       <c r="B4" s="1">
         <v>3</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="13">
         <f>B4*2</f>
         <v>6</v>
       </c>
@@ -1576,7 +1588,7 @@
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="13">
         <f t="shared" ref="C5:C30" si="0">B5*2</f>
         <v>2</v>
       </c>
@@ -1603,7 +1615,7 @@
       <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1630,7 +1642,7 @@
       <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1658,7 +1670,7 @@
       <c r="B8" s="1">
         <v>1</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1686,7 +1698,7 @@
       <c r="B9" s="1">
         <v>1</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1714,7 +1726,7 @@
       <c r="B10" s="1">
         <v>3</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="13">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1742,7 +1754,7 @@
       <c r="B11" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1770,7 +1782,7 @@
       <c r="B12" s="1">
         <v>1</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1798,7 +1810,7 @@
       <c r="B13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1826,7 +1838,7 @@
       <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1854,7 +1866,7 @@
       <c r="B15" s="1">
         <v>1</v>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1882,7 +1894,7 @@
       <c r="B16" s="1">
         <v>3</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="13">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -1910,7 +1922,7 @@
       <c r="B17" s="1">
         <v>1</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1938,7 +1950,7 @@
       <c r="B18" s="1">
         <v>5</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="13">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -1966,7 +1978,7 @@
       <c r="B19" s="1">
         <v>15</v>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="13">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -1994,7 +2006,7 @@
       <c r="B20" s="1">
         <v>3</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="13">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -2022,7 +2034,7 @@
       <c r="B21" s="1">
         <v>7</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="13">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -2050,7 +2062,7 @@
       <c r="B22" s="1">
         <v>1</v>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -2078,7 +2090,7 @@
       <c r="B23" s="1">
         <v>1</v>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -2106,7 +2118,7 @@
       <c r="B24" s="1">
         <v>1</v>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -2134,7 +2146,7 @@
       <c r="B25" s="1">
         <v>1</v>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -2162,7 +2174,7 @@
       <c r="B26" s="1">
         <v>2</v>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="13">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -2188,7 +2200,7 @@
       <c r="B27" s="1">
         <v>1</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -2214,7 +2226,7 @@
       <c r="B28" s="1">
         <v>2</v>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="13">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -2242,7 +2254,7 @@
       <c r="B29" s="1">
         <v>6</v>
       </c>
-      <c r="C29" s="18">
+      <c r="C29" s="13">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -2268,7 +2280,7 @@
       <c r="B30" s="1">
         <v>1</v>
       </c>
-      <c r="C30" s="18">
+      <c r="C30" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -2297,26 +2309,26 @@
       </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="6" t="s">
@@ -2325,7 +2337,7 @@
       <c r="B35" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="12" t="s">
         <v>99</v>
       </c>
       <c r="D35" s="6" t="s">
@@ -2351,7 +2363,7 @@
       <c r="B36" s="1">
         <v>1</v>
       </c>
-      <c r="C36" s="18">
+      <c r="C36" s="13">
         <v>2</v>
       </c>
       <c r="D36" s="1"/>
@@ -2377,26 +2389,26 @@
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
+      <c r="A40" s="15"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="2" t="s">
@@ -2405,7 +2417,7 @@
       <c r="B41" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="12" t="s">
         <v>99</v>
       </c>
       <c r="D41" s="6" t="s">
@@ -2429,11 +2441,11 @@
         <v>78</v>
       </c>
       <c r="B42" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="C42" s="18">
+        <v>0</v>
+      </c>
+      <c r="C42" s="13">
         <f>B42*2</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
@@ -2447,7 +2459,7 @@
       </c>
       <c r="H42" s="1">
         <f>G42*C42</f>
-        <v>97.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -2457,8 +2469,8 @@
       <c r="B43" s="1">
         <v>1</v>
       </c>
-      <c r="C43" s="18">
-        <f t="shared" ref="C43:C55" si="2">B43*2</f>
+      <c r="C43" s="13">
+        <f t="shared" ref="C43:C57" si="2">B43*2</f>
         <v>2</v>
       </c>
       <c r="D43" s="1"/>
@@ -2472,7 +2484,7 @@
         <v>7.53</v>
       </c>
       <c r="H43" s="1">
-        <f t="shared" ref="H43:H55" si="3">G43*C43</f>
+        <f t="shared" ref="H43:H57" si="3">G43*C43</f>
         <v>15.06</v>
       </c>
     </row>
@@ -2483,7 +2495,7 @@
       <c r="B44" s="1">
         <v>0.5</v>
       </c>
-      <c r="C44" s="18">
+      <c r="C44" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2509,7 +2521,7 @@
       <c r="B45" s="1">
         <v>1</v>
       </c>
-      <c r="C45" s="18">
+      <c r="C45" s="13">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
@@ -2535,7 +2547,7 @@
       <c r="B46" s="1">
         <v>0.5</v>
       </c>
-      <c r="C46" s="18">
+      <c r="C46" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2561,7 +2573,7 @@
       <c r="B47" s="1">
         <v>0.5</v>
       </c>
-      <c r="C47" s="18">
+      <c r="C47" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2587,7 +2599,7 @@
       <c r="B48" s="1">
         <v>0.5</v>
       </c>
-      <c r="C48" s="18">
+      <c r="C48" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2613,7 +2625,7 @@
       <c r="B49" s="1">
         <v>0.5</v>
       </c>
-      <c r="C49" s="18">
+      <c r="C49" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2639,7 +2651,7 @@
       <c r="B50" s="1">
         <v>0.5</v>
       </c>
-      <c r="C50" s="18">
+      <c r="C50" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2665,7 +2677,7 @@
       <c r="B51" s="1">
         <v>0.5</v>
       </c>
-      <c r="C51" s="18">
+      <c r="C51" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2691,7 +2703,7 @@
       <c r="B52" s="1">
         <v>0.5</v>
       </c>
-      <c r="C52" s="18">
+      <c r="C52" s="13">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -2717,7 +2729,7 @@
       <c r="B53" s="1">
         <v>4</v>
       </c>
-      <c r="C53" s="18">
+      <c r="C53" s="13">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
@@ -2737,27 +2749,27 @@
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="14" t="s">
+      <c r="A54" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B54" s="15">
-        <v>1</v>
-      </c>
-      <c r="C54" s="16">
+      <c r="B54" s="10">
+        <v>1</v>
+      </c>
+      <c r="C54" s="11">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D54" s="16"/>
-      <c r="E54" s="15" t="s">
+      <c r="D54" s="11"/>
+      <c r="E54" s="10" t="s">
         <v>77</v>
       </c>
       <c r="F54" t="s">
         <v>105</v>
       </c>
-      <c r="G54" s="15">
+      <c r="G54" s="10">
         <v>7.89</v>
       </c>
-      <c r="H54" s="15">
+      <c r="H54" s="10">
         <f t="shared" si="3"/>
         <v>15.78</v>
       </c>
@@ -2766,58 +2778,110 @@
       <c r="A55" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B55" s="15">
-        <v>1</v>
-      </c>
-      <c r="C55" s="16">
+      <c r="B55" s="10">
+        <v>1</v>
+      </c>
+      <c r="C55" s="11">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="D55" s="16"/>
-      <c r="E55" s="15" t="s">
+      <c r="D55" s="11"/>
+      <c r="E55" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F55" s="15" t="s">
+      <c r="F55" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="G55" s="15">
+      <c r="G55" s="10">
         <v>4.92</v>
       </c>
-      <c r="H55" s="15">
+      <c r="H55" s="10">
         <f t="shared" si="3"/>
         <v>9.84</v>
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="8"/>
+      <c r="A56" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B56" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="C56" s="11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D56" s="11"/>
+      <c r="E56" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="G56" s="10">
+        <v>21.89</v>
+      </c>
+      <c r="H56" s="10">
+        <f t="shared" si="3"/>
+        <v>21.89</v>
+      </c>
     </row>
     <row r="57" spans="1:8">
-      <c r="G57" s="5" t="s">
+      <c r="A57" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B57" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="C57" s="11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D57" s="11"/>
+      <c r="E57" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G57" s="10">
+        <v>9.83</v>
+      </c>
+      <c r="H57" s="10">
+        <f t="shared" si="3"/>
+        <v>9.83</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="8"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="G59" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H57" s="5">
-        <f>SUM(H42:H55)</f>
-        <v>699.83</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="F59" s="10" t="s">
+      <c r="H59" s="5">
+        <f>SUM(H42:H57)</f>
+        <v>634.20999999999992</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="F61" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="G59" s="11"/>
-      <c r="H59" s="3">
-        <f>H32+H38+H57</f>
-        <v>973.8900000000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="F60" s="12" t="s">
+      <c r="G61" s="17"/>
+      <c r="H61" s="3">
+        <f>H32+H38+H59</f>
+        <v>908.27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="F62" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="G60" s="13"/>
-      <c r="H60" s="4">
-        <f>H59*1.2</f>
-        <v>1168.6680000000001</v>
+      <c r="G62" s="19"/>
+      <c r="H62" s="4">
+        <f>H61*1.2</f>
+        <v>1089.924</v>
       </c>
     </row>
   </sheetData>
@@ -2825,8 +2889,8 @@
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A33:H34"/>
     <mergeCell ref="A39:H40"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F62:G62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Interface_IAI.xlsx
+++ b/Interface_IAI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Buloup\Documents\GIT\Interface_IAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A738DB8-9050-474F-BB1D-D3B5A4C78D7F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3A9CC6-EFAE-4699-94DD-C08D7B83BA37}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="116">
   <si>
     <t>Composants pour cicuit imprimé</t>
   </si>
@@ -352,49 +352,7 @@
     <t xml:space="preserve"> 175-3723</t>
   </si>
   <si>
-    <t>Filtre EMI (RS )</t>
-  </si>
-  <si>
     <t>292-818</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Filtre </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>EMI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>RS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t xml:space="preserve"> )</t>
-    </r>
   </si>
   <si>
     <t>708-4272</t>
@@ -521,6 +479,37 @@
   </si>
   <si>
     <t>Connecteur CEI Droit C19 Schurter, Câble</t>
+  </si>
+  <si>
+    <t>236-9258</t>
+  </si>
+  <si>
+    <t>Câble industriels multiconducteur (36 - 25m)</t>
+  </si>
+  <si>
+    <t>Filtre EMI 20A</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Filtre </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>EMI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> 10A</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1497,7 +1486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="45.109375" customWidth="1"/>
@@ -1533,13 +1522,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>2</v>
@@ -2275,7 +2264,7 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B30" s="1">
         <v>1</v>
@@ -2335,13 +2324,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>2</v>
@@ -2390,7 +2379,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -2415,13 +2404,13 @@
         <v>1</v>
       </c>
       <c r="B41" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D41" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>2</v>
@@ -2470,7 +2459,7 @@
         <v>1</v>
       </c>
       <c r="C43" s="13">
-        <f t="shared" ref="C43:C57" si="2">B43*2</f>
+        <f t="shared" ref="C43:C58" si="2">B43*2</f>
         <v>2</v>
       </c>
       <c r="D43" s="1"/>
@@ -2484,13 +2473,13 @@
         <v>7.53</v>
       </c>
       <c r="H43" s="1">
-        <f t="shared" ref="H43:H57" si="3">G43*C43</f>
+        <f t="shared" ref="H43:H58" si="3">G43*C43</f>
         <v>15.06</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B44" s="1">
         <v>0.5</v>
@@ -2516,7 +2505,7 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B45" s="1">
         <v>1</v>
@@ -2530,7 +2519,7 @@
         <v>77</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G45" s="1">
         <v>7.91</v>
@@ -2556,7 +2545,7 @@
         <v>77</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G46" s="1">
         <v>244.52</v>
@@ -2594,7 +2583,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B48" s="1">
         <v>0.5</v>
@@ -2620,7 +2609,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B49" s="1">
         <v>0.5</v>
@@ -2646,7 +2635,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B50" s="1">
         <v>0.5</v>
@@ -2672,7 +2661,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="7" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="B51" s="1">
         <v>0.5</v>
@@ -2686,7 +2675,7 @@
         <v>77</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G51" s="1">
         <v>67.75</v>
@@ -2698,7 +2687,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="7" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="B52" s="1">
         <v>0.5</v>
@@ -2712,7 +2701,7 @@
         <v>77</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G52" s="1">
         <v>52.9</v>
@@ -2724,7 +2713,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B53" s="1">
         <v>4</v>
@@ -2738,7 +2727,7 @@
         <v>77</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G53" s="1">
         <v>10.46</v>
@@ -2750,7 +2739,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B54" s="10">
         <v>1</v>
@@ -2764,7 +2753,7 @@
         <v>77</v>
       </c>
       <c r="F54" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G54" s="10">
         <v>7.89</v>
@@ -2776,7 +2765,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B55" s="10">
         <v>1</v>
@@ -2790,7 +2779,7 @@
         <v>77</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G55" s="10">
         <v>4.92</v>
@@ -2802,7 +2791,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B56" s="10">
         <v>0.5</v>
@@ -2816,7 +2805,7 @@
         <v>77</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G56" s="10">
         <v>21.89</v>
@@ -2828,7 +2817,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B57" s="10">
         <v>0.5</v>
@@ -2842,7 +2831,7 @@
         <v>77</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G57" s="10">
         <v>9.83</v>
@@ -2853,35 +2842,61 @@
       </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="8"/>
+      <c r="A58" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B58" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="C58" s="11">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="D58" s="11"/>
+      <c r="E58" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G58" s="10">
+        <v>181.19</v>
+      </c>
+      <c r="H58" s="10">
+        <f t="shared" si="3"/>
+        <v>181.19</v>
+      </c>
     </row>
     <row r="59" spans="1:8">
-      <c r="G59" s="5" t="s">
+      <c r="A59" s="8"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="G60" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H59" s="5">
-        <f>SUM(H42:H57)</f>
-        <v>634.20999999999992</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="F61" s="16" t="s">
+      <c r="H60" s="5">
+        <f>SUM(H42:H58)</f>
+        <v>815.39999999999986</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="F62" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="G61" s="17"/>
-      <c r="H61" s="3">
-        <f>H32+H38+H59</f>
-        <v>908.27</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="F62" s="18" t="s">
+      <c r="G62" s="17"/>
+      <c r="H62" s="3">
+        <f>H32+H38+H60</f>
+        <v>1089.46</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="F63" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="G62" s="19"/>
-      <c r="H62" s="4">
-        <f>H61*1.2</f>
-        <v>1089.924</v>
+      <c r="G63" s="19"/>
+      <c r="H63" s="4">
+        <f>H62*1.2</f>
+        <v>1307.3520000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2889,8 +2904,8 @@
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A33:H34"/>
     <mergeCell ref="A39:H40"/>
-    <mergeCell ref="F61:G61"/>
     <mergeCell ref="F62:G62"/>
+    <mergeCell ref="F63:G63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
